--- a/projects/xiuxian/game/data/table/建筑配置.xlsx
+++ b/projects/xiuxian/game/data/table/建筑配置.xlsx
@@ -575,7 +575,7 @@
         <v>20</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
         <v>35</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         <v>50</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
